--- a/output/pdf_financials_xlsx/VLN.xlsx
+++ b/output/pdf_financials_xlsx/VLN.xlsx
@@ -2143,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.8129999999999999</v>
+        <v>8.959</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>4.33</v>
+        <v>13.177</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -2204,10 +2204,10 @@
         <v>56.304</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>28.666</v>
+        <v>36.812</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10.109</v>
+        <v>18.956</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>11.387</v>
@@ -2265,10 +2265,10 @@
         <v>12.08382963654509</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>7.529694830131388</v>
+        <v>9.66940368683446</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2.312557905452549</v>
+        <v>4.336417811431251</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>2.27478854275292</v>
@@ -6487,10 +6487,10 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>8.959</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>13.177</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -7213,16 +7213,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>13.738</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>30.183</v>
       </c>
       <c r="P112" s="3" t="n">
         <v>0</v>
@@ -8069,37 +8069,37 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-0.119</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-1.774</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-0.948</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-0.041</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-0.103</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-1.033</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-0.139</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-0.049</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-0.041</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>-0.927</v>
       </c>
       <c r="M126" s="3" t="n">
         <v>0</v>
@@ -8108,7 +8108,7 @@
         <v>0</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0</v>
+        <v>-0.843</v>
       </c>
       <c r="P126" s="3" t="n">
         <v>0</v>
@@ -24298,7 +24298,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -28664,7 +28668,11 @@
           <t>Dividends paid to non-controlling interest</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -29056,7 +29064,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E207" s="5" t="n">
         <v>0.117</v>
       </c>
@@ -31694,7 +31706,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -33344,7 +33360,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -33450,7 +33470,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -36368,7 +36388,11 @@
           <t>Dividends to non-controlling interest</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E278" s="5" t="n">
         <v>-0.119</v>
       </c>

--- a/output/pdf_financials_xlsx/VLN.xlsx
+++ b/output/pdf_financials_xlsx/VLN.xlsx
@@ -2845,13 +2845,13 @@
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>13.157</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         <v>137.382</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>137.52</v>
+        <v>144.78</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>135.242</v>
+        <v>142.722</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>135.373</v>
+        <v>148.53</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>115.834</v>
@@ -3333,13 +3333,13 @@
         <v>183.628</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>21.664</v>
+        <v>14.404</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>9.209</v>
+        <v>1.729</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>12.664</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>10.385</v>
@@ -3830,55 +3830,55 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>166.825</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>172.158</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>195.203</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>217.649</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>234.333</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>230.748</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>243.068</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>245.679</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>257.438</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>252.284</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>272.05</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>264.219</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>236.65</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>229.302</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>237.292</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0</v>
+        <v>196.511</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>0</v>
+        <v>204.073</v>
       </c>
     </row>
     <row r="57">
@@ -3891,55 +3891,55 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>102.894</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>107.536</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>122.242</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>127.019</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>137.728</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>139.463</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>147.811</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>154.144</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>167.574</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>168.747</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>173.871</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>167.892</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>162.744</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>161.097</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>167.374</v>
       </c>
       <c r="R57" s="3" t="n">
-        <v>0</v>
+        <v>145.162</v>
       </c>
       <c r="S57" s="3" t="n">
-        <v>0</v>
+        <v>153.138</v>
       </c>
     </row>
     <row r="58">
@@ -4322,55 +4322,55 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>30.67</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>29.372</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>43.215</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>35.53</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>31.41</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>26.868</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>20.661</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>25.969</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>23.635</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>31.016</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>32.091</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>37.08</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>34.306</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>39.898</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>46.294</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>30.066</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>47.206</v>
       </c>
     </row>
     <row r="65">
@@ -4505,55 +4505,55 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>30.304</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>32.922</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>36.548</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>39.094</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>41.712</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>41.018</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>37.217</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>30.668</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>35.597</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>40.039</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>13.032</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>22.926</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>14.373</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>10.543</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>14.413</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>24.529</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>15.107</v>
       </c>
     </row>
     <row r="68">
@@ -6908,16 +6908,16 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0</v>
@@ -7764,40 +7764,40 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.047</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-1.056</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.481</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.605</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-2.633</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.306</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-2.738</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.926</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="L121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="N121" s="3" t="n">
         <v>0</v>
@@ -7886,55 +7886,55 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>1.001</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>5.221</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>21.057</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>2.654</v>
       </c>
       <c r="H123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>17.499</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>5.079</v>
       </c>
       <c r="K123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>3.989</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>0</v>
+        <v>1.122</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>0</v>
+        <v>18.195</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>0</v>
+        <v>7.874</v>
       </c>
       <c r="P123" s="3" t="n">
-        <v>0</v>
+        <v>3.666</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="R123" s="3" t="n">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="S123" s="3" t="n">
         <v>0</v>
@@ -8008,55 +8008,55 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-2.195</v>
+        <v>-1.947</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>-1.061</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-3.002</v>
+        <v>2.219</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-4.478</v>
+        <v>16.579</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-8.43</v>
+        <v>-5.776</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>-6.326</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-9.122</v>
+        <v>8.377000000000001</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-5.904</v>
+        <v>-0.825</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>-3.206</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-3.586</v>
+        <v>0.403</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-2.896</v>
+        <v>-1.774</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-3.643</v>
+        <v>14.552</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-6.722</v>
+        <v>1.152</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-4.398</v>
+        <v>-0.732</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>-8.896000000000001</v>
+        <v>-7.61</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>-4.163</v>
+        <v>-3.837</v>
       </c>
       <c r="S125" s="3" t="n">
         <v>-7.69</v>
@@ -9772,7 +9772,11 @@
           <t>Intangible assets and goodwill (note 11)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -12616,7 +12620,11 @@
           <t>Intangible assets and goodwill (note 9)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -15082,7 +15090,11 @@
           <t>Intangible assets and goodwill (notes 4 and 8)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -17082,7 +17094,11 @@
           <t>Intangible assets and goodwill (note 8)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -25100,7 +25116,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="n">
         <v>0.248</v>
       </c>
@@ -29560,7 +29580,11 @@
           <t>Repurchase of shares (note 14 (c))</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -30764,7 +30788,11 @@
           <t>Repurchase of shares (note 13 (c))</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -30968,7 +30996,11 @@
           <t>Increase in long-term debt (note 29)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -31814,7 +31846,11 @@
           <t>Repurchase of shares (note 13(c))</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -33684,7 +33720,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -34734,7 +34774,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E262" s="5" t="n">
         <v>1.036</v>
       </c>
@@ -34836,7 +34880,11 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E263" s="5" t="n">
         <v>0.103</v>
       </c>
@@ -36284,7 +36332,11 @@
           <t>Repurchase of shares (note 7(c))</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -37344,7 +37396,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E287" s="5" t="n">
         <v>-0.047</v>
       </c>
